--- a/02-PRD文档/后台管理/角色权限矩阵.xlsx
+++ b/02-PRD文档/后台管理/角色权限矩阵.xlsx
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>全权限：可查看 / 新增 / 删除 / 编辑</t>
+          <t>全权限:可查看 / 新增 / 删除 / 编辑</t>
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>部分权限：仅查看 或 查看+业务编辑（不含新增/删除）</t>
+          <t>部分权限:仅查看 或 查看+业务编辑(不含新增/删除)</t>
         </is>
       </c>
       <c r="C29" s="17" t="n"/>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>管理区域固定为全国,账号创建时不可修改(标注/质检/领域工程师)</t>
+          <t>管理区域固定为全国;表单不展示该字段,提交时系统默认写入(标注/质检/领域工程师)</t>
         </is>
       </c>
       <c r="C32" s="17" t="n"/>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>管理区域必填,账号创建时按业务范围具体选择(巡查/运营)</t>
+          <t>管理区域必填;表单展示该字段,需手动选择具体区域,可选全国(巡查/运营管理员)</t>
         </is>
       </c>
       <c r="C33" s="17" t="n"/>
@@ -1639,7 +1639,7 @@
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>3. 管理区域:标/质/领 固定全国(不可改);巡/运 必填具体区域(上级覆盖下级)。</t>
+          <t>3. 管理区域:标/质/领 表单不展示该字段(系统默认全国);巡/运 表单必填,手动选择具体区域,上级覆盖下级。</t>
         </is>
       </c>
     </row>

--- a/02-PRD文档/后台管理/角色权限矩阵.xlsx
+++ b/02-PRD文档/后台管理/角色权限矩阵.xlsx
@@ -83,7 +83,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -143,6 +143,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -249,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -300,6 +306,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -666,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -676,6 +685,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -703,20 +714,30 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>质检人员</t>
+          <t>一检人员</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>二检人员</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>三检人员</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>巡查人员</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>领域工程师</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>运营管理员</t>
         </is>
@@ -729,7 +750,7 @@
 管理区域</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
+      <c r="B3" s="18" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
           <t>固定全国</t>
@@ -740,17 +761,27 @@
           <t>固定全国</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>固定全国</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>固定全国</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>手动选择</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>固定全国</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>手动选择</t>
         </is>
@@ -783,7 +814,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>查</t>
         </is>
@@ -810,9 +851,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -820,7 +861,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -843,9 +894,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>查增删改</t>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -854,6 +905,16 @@
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>查增删改</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -885,12 +946,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>查增删改</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>查增删改</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -913,17 +984,27 @@
           <t>查</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>查增删改</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>查增删改</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -951,14 +1032,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -979,19 +1070,29 @@
           <t>查改</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>查改</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
+          <t>查改</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1012,9 +1113,9 @@
           <t>查</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
@@ -1022,7 +1123,17 @@
           <t>查</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -1059,7 +1170,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -1092,7 +1213,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -1125,7 +1256,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -1152,17 +1293,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -1185,17 +1336,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -1218,17 +1379,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -1251,17 +1422,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -1298,7 +1479,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -1331,7 +1522,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -1364,7 +1565,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -1397,7 +1608,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -1430,7 +1651,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -1462,12 +1693,22 @@
           <t>查</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>查增删改</t>
-        </is>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>查增删改</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
@@ -1495,17 +1736,28 @@
           <t>查</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>查增删改</t>
-        </is>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>查增删改</t>
-        </is>
-      </c>
-    </row>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>查增删改</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>查增删改</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
@@ -1528,7 +1780,9 @@
       <c r="D28" s="17" t="n"/>
       <c r="E28" s="17" t="n"/>
       <c r="F28" s="17" t="n"/>
-      <c r="G28" s="18" t="n"/>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="17" t="n"/>
+      <c r="I28" s="18" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
@@ -1545,7 +1799,9 @@
       <c r="D29" s="17" t="n"/>
       <c r="E29" s="17" t="n"/>
       <c r="F29" s="17" t="n"/>
-      <c r="G29" s="18" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="18" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
@@ -1562,7 +1818,9 @@
       <c r="D30" s="17" t="n"/>
       <c r="E30" s="17" t="n"/>
       <c r="F30" s="17" t="n"/>
-      <c r="G30" s="18" t="n"/>
+      <c r="G30" s="17" t="n"/>
+      <c r="H30" s="17" t="n"/>
+      <c r="I30" s="18" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="14" t="inlineStr">
@@ -1579,7 +1837,9 @@
       <c r="D31" s="17" t="n"/>
       <c r="E31" s="17" t="n"/>
       <c r="F31" s="17" t="n"/>
-      <c r="G31" s="18" t="n"/>
+      <c r="G31" s="17" t="n"/>
+      <c r="H31" s="17" t="n"/>
+      <c r="I31" s="18" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -1596,7 +1856,9 @@
       <c r="D32" s="17" t="n"/>
       <c r="E32" s="17" t="n"/>
       <c r="F32" s="17" t="n"/>
-      <c r="G32" s="18" t="n"/>
+      <c r="G32" s="17" t="n"/>
+      <c r="H32" s="17" t="n"/>
+      <c r="I32" s="18" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
@@ -1613,8 +1875,11 @@
       <c r="D33" s="17" t="n"/>
       <c r="E33" s="17" t="n"/>
       <c r="F33" s="17" t="n"/>
-      <c r="G33" s="18" t="n"/>
-    </row>
+      <c r="G33" s="17" t="n"/>
+      <c r="H33" s="17" t="n"/>
+      <c r="I33" s="18" t="n"/>
+    </row>
+    <row r="34"/>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="19" t="inlineStr">
         <is>
@@ -1625,7 +1890,7 @@
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>1. 5 角色:标注人员 / 质检人员 / 巡查人员 / 领域工程师 / 运营管理员(原数据管理人员职责并入运营)。</t>
+          <t>1. 7 角色:标注人员 / 一检人员 / 二检人员 / 三检人员 / 巡查人员 / 领域工程师 / 运营管理员(原数据管理人员职责并入运营)。</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1904,7 @@
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>3. 管理区域:标/质/领 表单不展示该字段(系统默认全国);巡/运 表单必填,手动选择具体区域,上级覆盖下级。</t>
+          <t>3. 管理区域:标/一检/二检/三检/领 表单不展示该字段(系统默认全国);巡/运 表单必填,手动选择具体区域,上级覆盖下级。</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1918,7 @@
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>5. 知识库(隐患库 / 法规库):标/质/巡 仅查;领域/运营 全权限。</t>
+          <t>5. 知识库(隐患库 / 法规库):标/一检/二检/三检/巡 仅查;领域/运营 全权限。</t>
         </is>
       </c>
     </row>
@@ -1687,31 +1952,31 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="A42:I42"/>
     <mergeCell ref="A19:A23"/>
-    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="A35:I35"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A38:I38"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="B28:I28"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A39:I39"/>
     <mergeCell ref="A7:A11"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A15:A18"/>
-    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="B32:I32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02-PRD文档/后台管理/角色权限矩阵.xlsx
+++ b/02-PRD文档/后台管理/角色权限矩阵.xlsx
@@ -2,88 +2,248 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色权限矩阵" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="31">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="微软雅黑"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="微软雅黑"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="微软雅黑"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="002E5395"/>
+      <color rgb="FF2E5395"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="微软雅黑"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="006F2D8C"/>
+      <color rgb="FF6F2D8C"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="微软雅黑"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="FF1F3864"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="微软雅黑"/>
+      <charset val="134"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="微软雅黑"/>
-      <color rgb="00999999"/>
+      <charset val="134"/>
+      <color rgb="FF999999"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="微软雅黑"/>
+      <charset val="134"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="微软雅黑"/>
+      <charset val="134"/>
       <b val="1"/>
       <i val="1"/>
-      <color rgb="00C65911"/>
+      <color rgb="FFC65911"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="微软雅黑"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="FFC00000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="44">
     <fill>
       <patternFill/>
     </fill>
@@ -92,67 +252,258 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008FAADC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAD7F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
+        <fgColor rgb="FF305496"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FAADC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAD7F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -162,48 +513,151 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00888888"/>
+        <color rgb="FF888888"/>
       </left>
       <right style="thin">
-        <color rgb="00888888"/>
+        <color rgb="FF888888"/>
       </right>
       <top style="thin">
-        <color rgb="00888888"/>
+        <color rgb="FF888888"/>
       </top>
       <bottom style="thin">
-        <color rgb="00888888"/>
+        <color rgb="FF888888"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00888888"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
+      <left/>
+      <right style="thin">
+        <color rgb="FF888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF888888"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF888888"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00888888"/>
+        <color rgb="FF888888"/>
       </left>
       <right style="thin">
-        <color rgb="00888888"/>
+        <color rgb="FF888888"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF888888"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF888888"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF888888"/>
       </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF888888"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF888888"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="00888888"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="00888888"/>
+        <color rgb="FFB2B2B2"/>
       </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
       <bottom style="thin">
-        <color rgb="00888888"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -211,7 +665,18 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00888888"/>
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF888888"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -219,43 +684,172 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00888888"/>
+        <color rgb="FF888888"/>
       </right>
       <top style="thin">
-        <color rgb="00888888"/>
+        <color rgb="FF888888"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF888888"/>
+      </left>
       <right/>
-      <top style="thin">
-        <color rgb="00888888"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00888888"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00888888"/>
-      </right>
-      <top style="thin">
-        <color rgb="00888888"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00888888"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="40" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -266,7 +860,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -288,8 +882,8 @@
     <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -299,20 +893,64 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -665,7 +1303,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -675,24 +1312,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I48"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="32.5" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5角色 × 22页面 操作权限矩阵（按实际导航 + 开发中页面）</t>
+          <t>7角色 × 26页面 操作权限矩阵（按实际导航）</t>
         </is>
       </c>
     </row>
@@ -750,7 +1381,7 @@
 管理区域</t>
         </is>
       </c>
-      <c r="B3" s="18" t="n"/>
+      <c r="B3" s="4" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
           <t>固定全国</t>
@@ -788,7 +1419,7 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="7" t="inlineStr"/>
+      <c r="A4" s="7" t="n"/>
       <c r="B4" s="8" t="inlineStr">
         <is>
           <t>首页</t>
@@ -928,7 +1559,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>任务分配</t>
+          <t>任务分配管理</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -1012,9 +1643,9 @@
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="13" t="n"/>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>标注任务列表/标注工作台（开发中）</t>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>标注任务列表</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -1047,80 +1678,80 @@
           <t>查</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="13" t="n"/>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>质检任务列表/质检工作台（开发中）</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>标注工作台</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>查改</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>质检任务列表</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>查改</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>查改</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="I10" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>高质量数据池（开发中）</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>查</t>
+          <t>查改</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -1133,21 +1764,17 @@
           <t>查</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>查增删改</t>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>订单中心</t>
-        </is>
-      </c>
+      <c r="A12" s="13" t="n"/>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>订单管理</t>
+          <t>质检工作台</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -1155,19 +1782,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>查改</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>查改</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>查改</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -1175,14 +1802,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>查增删改</t>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1817,7 @@
       <c r="A13" s="13" t="n"/>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>培训管理</t>
+          <t>评分记录列表</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -1218,112 +1845,112 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>人员评分统计</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="n"/>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>高质量数据池</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>巡检管理</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>查增删改</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>用户中心</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>巡检单位库</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>查增删改</t>
-        </is>
-      </c>
-    </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="13" t="n"/>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>订单中心</t>
+        </is>
+      </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>巡检人员库</t>
+          <t>订单管理</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1346,14 +1973,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
@@ -1366,7 +1993,7 @@
       <c r="A17" s="13" t="n"/>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>保险机构库</t>
+          <t>培训管理</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -1389,14 +2016,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
@@ -1409,7 +2036,7 @@
       <c r="A18" s="12" t="n"/>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>施工单位库</t>
+          <t>巡检管理</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -1432,14 +2059,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
@@ -1451,12 +2078,12 @@
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>系统管理</t>
+          <t>用户中心</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>导航管理</t>
+          <t>巡检单位库</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -1479,14 +2106,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
@@ -1499,7 +2126,7 @@
       <c r="A20" s="13" t="n"/>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>账号管理</t>
+          <t>巡检人员库</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -1522,14 +2149,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr">
@@ -1542,314 +2169,414 @@
       <c r="A21" s="13" t="n"/>
       <c r="B21" s="8" t="inlineStr">
         <is>
+          <t>保险机构库</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>查增删改</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="12" t="n"/>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>施工单位库</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>查增删改</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>系统管理</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>导航管理</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>查增删改</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>账号管理</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>查增删改</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
           <t>角色管理</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="13" t="n"/>
-      <c r="B22" s="8" t="inlineStr">
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>字典管理</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="8" t="inlineStr">
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="12" t="n"/>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>内容管理</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>知识库管理</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>隐患库管理</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="n"/>
-      <c r="B25" s="8" t="inlineStr">
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="12" t="n"/>
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>法规库管理</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>查</t>
-        </is>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="I29" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+    <row r="30" ht="24" customHeight="1"/>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>查增删改</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>全权限:可查看 / 新增 / 删除 / 编辑</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="n"/>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="17" t="n"/>
-      <c r="F28" s="17" t="n"/>
-      <c r="G28" s="17" t="n"/>
-      <c r="H28" s="17" t="n"/>
-      <c r="I28" s="18" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>查改 / 查</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>部分权限:仅查看 或 查看+业务编辑(不含新增/删除)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="17" t="n"/>
-      <c r="G29" s="17" t="n"/>
-      <c r="H29" s="17" t="n"/>
-      <c r="I29" s="18" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>无权限:默认不勾;勾选后按数据隔离规则呈现无数据</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="n"/>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="17" t="n"/>
-      <c r="F30" s="17" t="n"/>
-      <c r="G30" s="17" t="n"/>
-      <c r="H30" s="17" t="n"/>
-      <c r="I30" s="18" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>开发中</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>页面研发中尚未上线;权限规则已预定义,待页面发布后启用</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="n"/>
-      <c r="D31" s="17" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="17" t="n"/>
-      <c r="G31" s="17" t="n"/>
-      <c r="H31" s="17" t="n"/>
-      <c r="I31" s="18" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>固定全国</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>管理区域固定为全国;表单不展示该字段,提交时系统默认写入(标注/质检/领域工程师)</t>
         </is>
       </c>
       <c r="C32" s="17" t="n"/>
@@ -1858,17 +2585,17 @@
       <c r="F32" s="17" t="n"/>
       <c r="G32" s="17" t="n"/>
       <c r="H32" s="17" t="n"/>
-      <c r="I32" s="18" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>手动选择</t>
+      <c r="I32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>查改 / 查</t>
         </is>
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>管理区域必填;表单展示该字段,需手动选择具体区域,可选全国(巡查/运营管理员)</t>
+          <t>部分权限:仅查看 或 查看+业务编辑(不含新增/删除)</t>
         </is>
       </c>
       <c r="C33" s="17" t="n"/>
@@ -1877,106 +2604,184 @@
       <c r="F33" s="17" t="n"/>
       <c r="G33" s="17" t="n"/>
       <c r="H33" s="17" t="n"/>
-      <c r="I33" s="18" t="n"/>
-    </row>
-    <row r="34"/>
+      <c r="I33" s="4" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>无权限:默认不勾选;勾选后按数据隔离规则呈现无数据</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="17" t="n"/>
+      <c r="H34" s="17" t="n"/>
+      <c r="I34" s="4" t="n"/>
+    </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>正式页</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>新增业务页面按正式页面权限维护，不再区分开发中状态。</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
+      <c r="G35" s="17" t="n"/>
+      <c r="H35" s="17" t="n"/>
+      <c r="I35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>固定全国</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>管理区域固定为全国;表单不展示该字段,提交时系统默认写入(标注/质检/领域工程师)</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
+      <c r="G36" s="17" t="n"/>
+      <c r="H36" s="17" t="n"/>
+      <c r="I36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>手动选择</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>管理区域必填;表单展示该字段,需手动选择具体区域,可选全国(巡查/运营管理员)</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
+      <c r="G37" s="17" t="n"/>
+      <c r="H37" s="17" t="n"/>
+      <c r="I37" s="4" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1"/>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>1. 7 角色:标注人员 / 一检人员 / 二检人员 / 三检人员 / 巡查人员 / 领域工程师 / 运营管理员(原数据管理人员职责并入运营)。</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>2. 数据可见范围 = 角色类型 + 管理区域 双重约束,勾选页面权限不代表有数据。</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>3. 管理区域:标/一检/二检/三检/领 表单不展示该字段(系统默认全国);巡/运 表单必填,手动选择具体区域,上级覆盖下级。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>3. 管理区域:标/一检/二检/三检/领域 表单不展示该字段(系统默认全国);巡查/运营 表单必填,手动选择具体区域,上级覆盖下级。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>4. 首页(仪表盘)当前仅运营,后续按角色细分(待落地)。</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>5. 知识库(隐患库 / 法规库):标/一检/二检/三检/巡 仅查;领域/运营 全权限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>5. 知识库(隐患库 / 法规库):标/一检/二检/三检/巡查 仅查;领域/运营 全权限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>6. 标注/质检工作台:运营仅查不改(不代写标注/质检结果)。</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>7. 用户中心业务对象库(巡检单位/人员/保险/施工):巡查/领域 仅查;运营 全权限。</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>8. 橙色行(标注/质检任务列表/工作台、高质量数据池) = 开发中,上线后启用预设权限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>8. 标注质检新增业务页面均按正式页面逐行维护权限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>9. 操作日志 当前系统未规划。</t>
         </is>
       </c>
     </row>
+    <row r="49" ht="22" customHeight="1"/>
+    <row r="50" ht="22" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
     <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A23:A27"/>
+    <mergeCell ref="A47:I47"/>
     <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A19:A23"/>
-    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="B32:I32"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A38:I38"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A43:I43"/>
-    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="B34:I34"/>
     <mergeCell ref="A44:I44"/>
-    <mergeCell ref="B28:I28"/>
     <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="B37:I37"/>
     <mergeCell ref="A39:I39"/>
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A48:I48"/>
     <mergeCell ref="B33:I33"/>
-    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A45:I45"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="A7:A15"/>
+    <mergeCell ref="B35:I35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
